--- a/exports/trend_1d/UPL_full_report.xlsx
+++ b/exports/trend_1d/UPL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.43</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H2" t="n">
-        <v>274.3</v>
+        <v>262.1</v>
       </c>
       <c r="I2" t="n">
         <v>269.5105499802303</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K2" t="n">
-        <v>18.33</v>
+        <v>13.07</v>
       </c>
       <c r="L2" t="n">
         <v>3.73</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>16.44</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42123</v>
+        <v>42124</v>
       </c>
       <c r="H3" t="n">
-        <v>299.7</v>
+        <v>313.75</v>
       </c>
       <c r="I3" t="n">
         <v>305.1829031579709</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-14.35</v>
+        <v>-19.71</v>
       </c>
       <c r="L3" t="n">
-        <v>17.89</v>
+        <v>21</v>
       </c>
       <c r="M3" t="n">
         <v>0.8100000000000001</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>16.16</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>342.6</v>
+        <v>312.4</v>
       </c>
       <c r="I4" t="n">
         <v>329.2023136029901</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K4" t="n">
-        <v>9.199999999999999</v>
+        <v>-0.43</v>
       </c>
       <c r="L4" t="n">
-        <v>5.78</v>
+        <v>7.06</v>
       </c>
       <c r="M4" t="n">
         <v>3.23</v>
       </c>
       <c r="N4" t="n">
-        <v>4.99</v>
+        <v>8.81</v>
       </c>
       <c r="O4" t="n">
         <v>4.69</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.49</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42362</v>
+        <v>42366</v>
       </c>
       <c r="H5" t="n">
-        <v>276.95</v>
+        <v>278.1</v>
       </c>
       <c r="I5" t="n">
         <v>277.9635248649889</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K5" t="n">
-        <v>11.35</v>
+        <v>10.98</v>
       </c>
       <c r="L5" t="n">
         <v>12.87</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>8.5</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42382</v>
+        <v>42383</v>
       </c>
       <c r="H6" t="n">
-        <v>262.9</v>
+        <v>254.85</v>
       </c>
       <c r="I6" t="n">
         <v>259.7514598946895</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.47</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>7.03</v>
+        <v>9.94</v>
       </c>
       <c r="M6" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="N6" t="n">
         <v>5.86</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>11.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H7" t="n">
-        <v>262.6</v>
+        <v>279.55</v>
       </c>
       <c r="I7" t="n">
         <v>270.3585968618028</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.04</v>
+        <v>-9.69</v>
       </c>
       <c r="L7" t="n">
-        <v>5.63</v>
+        <v>10.12</v>
       </c>
       <c r="M7" t="n">
         <v>1.3</v>
       </c>
       <c r="N7" t="n">
-        <v>5.69</v>
+        <v>6.45</v>
       </c>
       <c r="O7" t="n">
         <v>-3.06</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>14.14</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H8" t="n">
-        <v>252.8</v>
+        <v>247.9</v>
       </c>
       <c r="I8" t="n">
         <v>248.2384996001667</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.57</v>
+        <v>-11.32</v>
       </c>
       <c r="L8" t="n">
-        <v>12.11</v>
+        <v>13.81</v>
       </c>
       <c r="M8" t="n">
         <v>1.69</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.96</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>271.6</v>
+        <v>284.45</v>
       </c>
       <c r="I9" t="n">
         <v>274.6212845660837</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.56</v>
+        <v>-14.74</v>
       </c>
       <c r="L9" t="n">
-        <v>10.15</v>
+        <v>15.61</v>
       </c>
       <c r="M9" t="n">
         <v>3.04</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>14.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42541</v>
+        <v>42542</v>
       </c>
       <c r="H10" t="n">
-        <v>363.9</v>
+        <v>359.1</v>
       </c>
       <c r="I10" t="n">
         <v>359.5236578937063</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K10" t="n">
-        <v>27.93</v>
+        <v>26.24</v>
       </c>
       <c r="L10" t="n">
         <v>5.57</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42572</v>
+        <v>42573</v>
       </c>
       <c r="H11" t="n">
-        <v>357.55</v>
+        <v>373.55</v>
       </c>
       <c r="I11" t="n">
         <v>367.2312596240039</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" t="n">
-        <v>0.43</v>
+        <v>-4.02</v>
       </c>
       <c r="L11" t="n">
-        <v>2.26</v>
+        <v>4.36</v>
       </c>
       <c r="M11" t="n">
         <v>0.68</v>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>4.47</v>
       </c>
       <c r="O11" t="n">
         <v>-1.32</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42678</v>
+        <v>42681</v>
       </c>
       <c r="H12" t="n">
-        <v>430.05</v>
+        <v>427.4</v>
       </c>
       <c r="I12" t="n">
         <v>427.8004556084204</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K12" t="n">
-        <v>15.13</v>
+        <v>14.42</v>
       </c>
       <c r="L12" t="n">
         <v>4.07</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>10.58</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42711</v>
+        <v>42712</v>
       </c>
       <c r="H13" t="n">
-        <v>429.9</v>
+        <v>447.75</v>
       </c>
       <c r="I13" t="n">
         <v>440.714635781255</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.58</v>
+        <v>-4.76</v>
       </c>
       <c r="L13" t="n">
-        <v>5.23</v>
+        <v>5.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.58</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>11.08</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42724</v>
+        <v>42725</v>
       </c>
       <c r="H14" t="n">
-        <v>405.6</v>
+        <v>403.6</v>
       </c>
       <c r="I14" t="n">
         <v>405.4017027568914</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.41</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>9.92</v>
+        <v>10.69</v>
       </c>
       <c r="M14" t="n">
         <v>2.01</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>10.77</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42746</v>
+        <v>42747</v>
       </c>
       <c r="H15" t="n">
-        <v>427.95</v>
+        <v>438.4</v>
       </c>
       <c r="I15" t="n">
         <v>437.4262569653404</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.03</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>7.74</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.42</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H16" t="n">
-        <v>552.1</v>
+        <v>531.1</v>
       </c>
       <c r="I16" t="n">
         <v>536.1839056375496</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K16" t="n">
-        <v>25.94</v>
+        <v>21.15</v>
       </c>
       <c r="L16" t="n">
         <v>2.84</v>
@@ -1353,7 +1544,7 @@
         <v>1.27</v>
       </c>
       <c r="N16" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>2.44</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="H17" t="n">
-        <v>519.9</v>
+        <v>531.6</v>
       </c>
       <c r="I17" t="n">
         <v>529.2980555512801</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K17" t="n">
-        <v>2.11</v>
+        <v>-0.09</v>
       </c>
       <c r="L17" t="n">
         <v>5.9</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43042</v>
+        <v>43045</v>
       </c>
       <c r="H18" t="n">
-        <v>496</v>
+        <v>487.25</v>
       </c>
       <c r="I18" t="n">
         <v>491.1887547826262</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.7</v>
+        <v>-8.34</v>
       </c>
       <c r="L18" t="n">
-        <v>7.08</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.94</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43096</v>
+        <v>43097</v>
       </c>
       <c r="H19" t="n">
-        <v>473.45</v>
+        <v>488.1</v>
       </c>
       <c r="I19" t="n">
         <v>483.7433378123612</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K19" t="n">
-        <v>2.83</v>
+        <v>-0.17</v>
       </c>
       <c r="L19" t="n">
         <v>2.61</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H20" t="n">
-        <v>492.9</v>
+        <v>480.9</v>
       </c>
       <c r="I20" t="n">
         <v>482.8877496460934</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>0.98</v>
+        <v>-1.48</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.41</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H21" t="n">
-        <v>467</v>
+        <v>481.15</v>
       </c>
       <c r="I21" t="n">
         <v>475.8422368375085</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K21" t="n">
-        <v>2.89</v>
+        <v>-0.05</v>
       </c>
       <c r="L21" t="n">
         <v>3.33</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43222</v>
+        <v>43223</v>
       </c>
       <c r="H22" t="n">
-        <v>469</v>
+        <v>452.7</v>
       </c>
       <c r="I22" t="n">
         <v>456.2615757603176</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.53</v>
+        <v>-5.91</v>
       </c>
       <c r="L22" t="n">
-        <v>3.63</v>
+        <v>6.39</v>
       </c>
       <c r="M22" t="n">
         <v>0.54</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.82</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43301</v>
+        <v>43304</v>
       </c>
       <c r="H23" t="n">
-        <v>351.45</v>
+        <v>404.25</v>
       </c>
       <c r="I23" t="n">
         <v>389.0026325793548</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>22.37</v>
+        <v>10.7</v>
       </c>
       <c r="L23" t="n">
         <v>5.94</v>
       </c>
       <c r="M23" t="n">
-        <v>1.21</v>
+        <v>4.23</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>15.02</v>
       </c>
       <c r="O23" t="n">
         <v>-3.48</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>17.82</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H24" t="n">
-        <v>425.75</v>
+        <v>416.55</v>
       </c>
       <c r="I24" t="n">
         <v>422.341787108166</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K24" t="n">
-        <v>5.32</v>
+        <v>3.04</v>
       </c>
       <c r="L24" t="n">
         <v>11.24</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>16.25</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H25" t="n">
-        <v>431.25</v>
+        <v>445.05</v>
       </c>
       <c r="I25" t="n">
         <v>440.042135733876</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.53</v>
+        <v>-6.84</v>
       </c>
       <c r="L25" t="n">
         <v>8.23</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>14.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43634</v>
+        <v>43635</v>
       </c>
       <c r="H26" t="n">
-        <v>639.3</v>
+        <v>607.75</v>
       </c>
       <c r="I26" t="n">
         <v>609.8677292608146</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K26" t="n">
-        <v>43.65</v>
+        <v>36.56</v>
       </c>
       <c r="L26" t="n">
         <v>3.73</v>
@@ -1923,7 +2234,7 @@
         <v>2.33</v>
       </c>
       <c r="N26" t="n">
-        <v>4.47</v>
+        <v>4.94</v>
       </c>
       <c r="O26" t="n">
         <v>3.2</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.13</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43649</v>
+        <v>43650</v>
       </c>
       <c r="H27" t="n">
-        <v>625.25</v>
+        <v>669.9</v>
       </c>
       <c r="I27" t="n">
         <v>638.4177277439035</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.88</v>
+        <v>-10.23</v>
       </c>
       <c r="L27" t="n">
-        <v>5.83</v>
+        <v>11.43</v>
       </c>
       <c r="M27" t="n">
         <v>1.49</v>
       </c>
       <c r="N27" t="n">
-        <v>5.22</v>
+        <v>7.14</v>
       </c>
       <c r="O27" t="n">
         <v>-4.94</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>14.15</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43672</v>
+        <v>43675</v>
       </c>
       <c r="H28" t="n">
-        <v>577.05</v>
+        <v>560.75</v>
       </c>
       <c r="I28" t="n">
         <v>575.1244170279343</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" t="n">
-        <v>-13.86</v>
+        <v>-16.29</v>
       </c>
       <c r="L28" t="n">
-        <v>15.66</v>
+        <v>16.88</v>
       </c>
       <c r="M28" t="n">
         <v>0.79</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>14.01</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43735</v>
+        <v>43738</v>
       </c>
       <c r="H29" t="n">
-        <v>558.35</v>
+        <v>579.35</v>
       </c>
       <c r="I29" t="n">
         <v>576.0394716022032</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K29" t="n">
-        <v>0.43</v>
+        <v>-3.32</v>
       </c>
       <c r="L29" t="n">
-        <v>3.45</v>
+        <v>3.98</v>
       </c>
       <c r="M29" t="n">
         <v>1.37</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>11.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43776</v>
+        <v>43777</v>
       </c>
       <c r="H30" t="n">
-        <v>554.15</v>
+        <v>533.2</v>
       </c>
       <c r="I30" t="n">
         <v>539.8337624667975</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.35</v>
+        <v>-7.97</v>
       </c>
       <c r="L30" t="n">
-        <v>7.76</v>
+        <v>8.51</v>
       </c>
       <c r="M30" t="n">
-        <v>1.16</v>
+        <v>2.44</v>
       </c>
       <c r="N30" t="n">
         <v>4.77</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.21</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43826</v>
+        <v>43829</v>
       </c>
       <c r="H31" t="n">
-        <v>556.6</v>
+        <v>565.35</v>
       </c>
       <c r="I31" t="n">
         <v>564.1138215908827</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.39</v>
+        <v>-6.03</v>
       </c>
       <c r="L31" t="n">
         <v>7.26</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43851</v>
+        <v>43852</v>
       </c>
       <c r="H32" t="n">
-        <v>554.15</v>
+        <v>540</v>
       </c>
       <c r="I32" t="n">
         <v>540.1759367818074</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.98</v>
+        <v>-4.48</v>
       </c>
       <c r="L32" t="n">
-        <v>2.91</v>
+        <v>6.1</v>
       </c>
       <c r="M32" t="n">
         <v>1.56</v>
       </c>
       <c r="N32" t="n">
-        <v>1.42</v>
+        <v>2.55</v>
       </c>
       <c r="O32" t="n">
         <v>1.57</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43868</v>
+        <v>43871</v>
       </c>
       <c r="H33" t="n">
-        <v>520.95</v>
+        <v>550.7</v>
       </c>
       <c r="I33" t="n">
         <v>541.2402189531721</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>3.53</v>
+        <v>-1.98</v>
       </c>
       <c r="L33" t="n">
         <v>3.54</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3</v>
+        <v>5.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>5.71</v>
       </c>
       <c r="O33" t="n">
         <v>-2.55</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>11.07</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H34" t="n">
-        <v>528.4</v>
+        <v>498.5</v>
       </c>
       <c r="I34" t="n">
         <v>520.2020101067956</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.05</v>
+        <v>-9.48</v>
       </c>
       <c r="L34" t="n">
-        <v>4.39</v>
+        <v>10.47</v>
       </c>
       <c r="M34" t="n">
-        <v>0.51</v>
+        <v>1.43</v>
       </c>
       <c r="N34" t="n">
-        <v>2.16</v>
+        <v>5.66</v>
       </c>
       <c r="O34" t="n">
         <v>5.71</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.88</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H35" t="n">
-        <v>345.9</v>
+        <v>402.95</v>
       </c>
       <c r="I35" t="n">
         <v>355.4775840381249</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K35" t="n">
-        <v>30.61</v>
+        <v>19.17</v>
       </c>
       <c r="L35" t="n">
         <v>5.18</v>
@@ -2436,7 +2855,7 @@
         <v>4.82</v>
       </c>
       <c r="N35" t="n">
-        <v>11.74</v>
+        <v>16.49</v>
       </c>
       <c r="O35" t="n">
         <v>-5.66</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>24.6</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44119</v>
+        <v>44120</v>
       </c>
       <c r="H36" t="n">
-        <v>485.9</v>
+        <v>447.9</v>
       </c>
       <c r="I36" t="n">
         <v>465.0383796439837</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K36" t="n">
-        <v>20.59</v>
+        <v>11.16</v>
       </c>
       <c r="L36" t="n">
         <v>20.01</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.79</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44167</v>
+        <v>44168</v>
       </c>
       <c r="H37" t="n">
-        <v>423.95</v>
+        <v>436.2</v>
       </c>
       <c r="I37" t="n">
         <v>434.369019350091</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" t="n">
-        <v>5.35</v>
+        <v>2.61</v>
       </c>
       <c r="L37" t="n">
         <v>4.95</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44174</v>
+        <v>44175</v>
       </c>
       <c r="H38" t="n">
-        <v>472.5</v>
+        <v>420.6</v>
       </c>
       <c r="I38" t="n">
         <v>421.5238826456803</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>8.32</v>
+        <v>-3.58</v>
       </c>
       <c r="L38" t="n">
-        <v>3.79</v>
+        <v>8.49</v>
       </c>
       <c r="M38" t="n">
-        <v>0.16</v>
+        <v>2.96</v>
       </c>
       <c r="N38" t="n">
-        <v>0.66</v>
+        <v>10.98</v>
       </c>
       <c r="O38" t="n">
         <v>2.89</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>16.67</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44203</v>
+        <v>44204</v>
       </c>
       <c r="H39" t="n">
-        <v>462.85</v>
+        <v>483.1</v>
       </c>
       <c r="I39" t="n">
         <v>476.3746269864819</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.05</v>
+        <v>-14.86</v>
       </c>
       <c r="L39" t="n">
-        <v>10.95</v>
+        <v>15.41</v>
       </c>
       <c r="M39" t="n">
         <v>3.99</v>
       </c>
       <c r="N39" t="n">
-        <v>2.73</v>
+        <v>4.38</v>
       </c>
       <c r="O39" t="n">
         <v>-10.98</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.61</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44365</v>
+        <v>44368</v>
       </c>
       <c r="H40" t="n">
-        <v>775.05</v>
+        <v>740.75</v>
       </c>
       <c r="I40" t="n">
         <v>751.2021826159415</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K40" t="n">
-        <v>60.43</v>
+        <v>53.33</v>
       </c>
       <c r="L40" t="n">
         <v>3.82</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.33</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="H41" t="n">
-        <v>715.95</v>
+        <v>739.85</v>
       </c>
       <c r="I41" t="n">
         <v>725.0990075876186</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K41" t="n">
-        <v>3.35</v>
+        <v>0.12</v>
       </c>
       <c r="L41" t="n">
         <v>10.38</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.61</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H42" t="n">
-        <v>711.25</v>
+        <v>687.3</v>
       </c>
       <c r="I42" t="n">
         <v>694.1564848458873</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.87</v>
+        <v>-7.1</v>
       </c>
       <c r="L42" t="n">
-        <v>4.05</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M42" t="n">
         <v>0.39</v>
       </c>
       <c r="N42" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="O42" t="n">
         <v>3.34</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.2</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44554</v>
+        <v>44557</v>
       </c>
       <c r="H43" t="n">
-        <v>716.4</v>
+        <v>725.75</v>
       </c>
       <c r="I43" t="n">
         <v>724.2658931038667</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.23</v>
+        <v>-5.59</v>
       </c>
       <c r="L43" t="n">
-        <v>5.93</v>
+        <v>6.07</v>
       </c>
       <c r="M43" t="n">
         <v>1.18</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>8.57</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H44" t="n">
-        <v>754.85</v>
+        <v>731.5</v>
       </c>
       <c r="I44" t="n">
         <v>747.3790880633949</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K44" t="n">
-        <v>4.01</v>
+        <v>0.79</v>
       </c>
       <c r="L44" t="n">
         <v>2.16</v>
       </c>
       <c r="M44" t="n">
-        <v>0.92</v>
+        <v>1.3</v>
       </c>
       <c r="N44" t="n">
         <v>3.11</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.68</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44624</v>
+        <v>44627</v>
       </c>
       <c r="H45" t="n">
-        <v>684.65</v>
+        <v>702.05</v>
       </c>
       <c r="I45" t="n">
         <v>698.6234188165312</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
-        <v>6.4</v>
+        <v>4.03</v>
       </c>
       <c r="L45" t="n">
         <v>6.58</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>15.65</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44692</v>
+        <v>44693</v>
       </c>
       <c r="H46" t="n">
-        <v>759.85</v>
+        <v>733.75</v>
       </c>
       <c r="I46" t="n">
         <v>737.7508851463693</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K46" t="n">
-        <v>8.23</v>
+        <v>4.52</v>
       </c>
       <c r="L46" t="n">
         <v>6.3</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.36</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H47" t="n">
-        <v>658.3</v>
+        <v>676.25</v>
       </c>
       <c r="I47" t="n">
         <v>673.2362194851604</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K47" t="n">
-        <v>10.28</v>
+        <v>7.84</v>
       </c>
       <c r="L47" t="n">
         <v>8.25</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.51</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H48" t="n">
-        <v>712.35</v>
+        <v>674.75</v>
       </c>
       <c r="I48" t="n">
         <v>706.9920891484484</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K48" t="n">
-        <v>5.34</v>
+        <v>-0.22</v>
       </c>
       <c r="L48" t="n">
         <v>2.77</v>
@@ -3177,7 +3752,7 @@
         <v>1.56</v>
       </c>
       <c r="N48" t="n">
-        <v>3.62</v>
+        <v>5.28</v>
       </c>
       <c r="O48" t="n">
         <v>2.73</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.94</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H49" t="n">
-        <v>684.8</v>
+        <v>700.45</v>
       </c>
       <c r="I49" t="n">
         <v>695.7708490958019</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.49</v>
+        <v>-3.81</v>
       </c>
       <c r="L49" t="n">
         <v>7.08</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H50" t="n">
-        <v>724.15</v>
+        <v>699.6</v>
       </c>
       <c r="I50" t="n">
         <v>720.0546179306099</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K50" t="n">
-        <v>3.38</v>
+        <v>-0.12</v>
       </c>
       <c r="L50" t="n">
         <v>2.63</v>
@@ -3291,7 +3890,7 @@
         <v>1.23</v>
       </c>
       <c r="N50" t="n">
-        <v>1.98</v>
+        <v>3.39</v>
       </c>
       <c r="O50" t="n">
         <v>2.29</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.65</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45044</v>
+        <v>45048</v>
       </c>
       <c r="H51" t="n">
-        <v>710.15</v>
+        <v>721.85</v>
       </c>
       <c r="I51" t="n">
         <v>716.2043632718887</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.51</v>
+        <v>-3.18</v>
       </c>
       <c r="L51" t="n">
         <v>6.95</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>6</v>
+      </c>
+      <c r="U51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.75</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45054</v>
+        <v>45055</v>
       </c>
       <c r="H52" t="n">
-        <v>686.25</v>
+        <v>666.1</v>
       </c>
       <c r="I52" t="n">
         <v>680.3142181393349</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.93</v>
+        <v>-7.72</v>
       </c>
       <c r="L52" t="n">
-        <v>6.92</v>
+        <v>7.96</v>
       </c>
       <c r="M52" t="n">
-        <v>0.14</v>
+        <v>0.76</v>
       </c>
       <c r="N52" t="n">
-        <v>2.28</v>
+        <v>2.94</v>
       </c>
       <c r="O52" t="n">
         <v>1.65</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H53" t="n">
-        <v>582.05</v>
+        <v>592.75</v>
       </c>
       <c r="I53" t="n">
         <v>588.4717871471362</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K53" t="n">
-        <v>12.62</v>
+        <v>11.01</v>
       </c>
       <c r="L53" t="n">
         <v>2.24</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5</v>
+      </c>
+      <c r="U53" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.58</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H54" t="n">
-        <v>578.85</v>
+        <v>562.8</v>
       </c>
       <c r="I54" t="n">
         <v>574.1872756840233</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.35</v>
+        <v>-5.05</v>
       </c>
       <c r="L54" t="n">
-        <v>3.26</v>
+        <v>5.31</v>
       </c>
       <c r="M54" t="n">
         <v>0.99</v>
       </c>
       <c r="N54" t="n">
-        <v>2.18</v>
+        <v>2.77</v>
       </c>
       <c r="O54" t="n">
         <v>1.84</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.02</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="H55" t="n">
-        <v>555.3</v>
+        <v>557.7</v>
       </c>
       <c r="I55" t="n">
         <v>555.4213561299219</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K55" t="n">
-        <v>1.33</v>
+        <v>0.91</v>
       </c>
       <c r="L55" t="n">
         <v>3.62</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.62</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H56" t="n">
-        <v>574.35</v>
+        <v>548.85</v>
       </c>
       <c r="I56" t="n">
         <v>554.3813519763111</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K56" t="n">
-        <v>2.99</v>
+        <v>-1.59</v>
       </c>
       <c r="L56" t="n">
-        <v>0.78</v>
+        <v>2.13</v>
       </c>
       <c r="M56" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>1.29</v>
+        <v>4.44</v>
       </c>
       <c r="O56" t="n">
         <v>0.43</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>9.67</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="H57" t="n">
-        <v>472.85</v>
+        <v>474.2</v>
       </c>
       <c r="I57" t="n">
         <v>473.5424119163953</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K57" t="n">
-        <v>13.85</v>
+        <v>13.6</v>
       </c>
       <c r="L57" t="n">
         <v>5.74</v>
       </c>
       <c r="M57" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="N57" t="n">
         <v>4.51</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.08</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H58" t="n">
-        <v>463.7</v>
+        <v>454.8</v>
       </c>
       <c r="I58" t="n">
         <v>456.1031825310339</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.21</v>
+        <v>-4.09</v>
       </c>
       <c r="L58" t="n">
         <v>5.62</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.99</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="H59" t="n">
-        <v>481.45</v>
+        <v>512.35</v>
       </c>
       <c r="I59" t="n">
         <v>491.2101396225248</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.86</v>
+        <v>-12.65</v>
       </c>
       <c r="L59" t="n">
-        <v>6.51</v>
+        <v>13.9</v>
       </c>
       <c r="M59" t="n">
         <v>0.97</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>12.49</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H60" t="n">
-        <v>515.15</v>
+        <v>507.85</v>
       </c>
       <c r="I60" t="n">
         <v>510.423946777235</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K60" t="n">
-        <v>0.55</v>
+        <v>-0.88</v>
       </c>
       <c r="L60" t="n">
         <v>10.51</v>
       </c>
       <c r="M60" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N60" t="n">
         <v>6.09</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.57</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45525</v>
+        <v>45526</v>
       </c>
       <c r="H61" t="n">
-        <v>545.15</v>
+        <v>555.55</v>
       </c>
       <c r="I61" t="n">
         <v>551.3847737439617</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.34</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>8.99</v>
+        <v>11.05</v>
       </c>
       <c r="M61" t="n">
         <v>1.96</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45572</v>
+        <v>45573</v>
       </c>
       <c r="H62" t="n">
-        <v>556.65</v>
+        <v>553.3</v>
       </c>
       <c r="I62" t="n">
         <v>553.7563459353312</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2</v>
+        <v>-0.41</v>
       </c>
       <c r="L62" t="n">
         <v>1.88</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.66</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H63" t="n">
-        <v>555.05</v>
+        <v>563.1</v>
       </c>
       <c r="I63" t="n">
         <v>557.5508334672262</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.32</v>
+        <v>-1.77</v>
       </c>
       <c r="L63" t="n">
         <v>2.92</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>9.98</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H64" t="n">
-        <v>518.35</v>
+        <v>504.5</v>
       </c>
       <c r="I64" t="n">
         <v>517.2154197875365</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.95</v>
+        <v>-10.41</v>
       </c>
       <c r="L64" t="n">
-        <v>8.119999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="M64" t="n">
         <v>1.55</v>
       </c>
       <c r="N64" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="O64" t="n">
         <v>1.45</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>10.43</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="H65" t="n">
-        <v>521.3</v>
+        <v>544.45</v>
       </c>
       <c r="I65" t="n">
         <v>539.8293804966215</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.33</v>
+        <v>-7.92</v>
       </c>
       <c r="L65" t="n">
-        <v>6.13</v>
+        <v>8.75</v>
       </c>
       <c r="M65" t="n">
         <v>0.32</v>
       </c>
       <c r="N65" t="n">
-        <v>3.95</v>
+        <v>4.44</v>
       </c>
       <c r="O65" t="n">
         <v>-2.67</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.84</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45806</v>
+        <v>45807</v>
       </c>
       <c r="H66" t="n">
-        <v>631</v>
+        <v>627.9</v>
       </c>
       <c r="I66" t="n">
         <v>628.6962639565735</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K66" t="n">
-        <v>15.9</v>
+        <v>15.33</v>
       </c>
       <c r="L66" t="n">
         <v>4.49</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>6</v>
+      </c>
+      <c r="U66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.88</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="H67" t="n">
-        <v>661.25</v>
+        <v>671.05</v>
       </c>
       <c r="I67" t="n">
         <v>667.6529389506559</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.31</v>
+        <v>-6.87</v>
       </c>
       <c r="L67" t="n">
-        <v>5.83</v>
+        <v>7.49</v>
       </c>
       <c r="M67" t="n">
         <v>1.11</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.67</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H68" t="n">
-        <v>703.8</v>
+        <v>665.15</v>
       </c>
       <c r="I68" t="n">
         <v>681.6928708544165</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K68" t="n">
-        <v>4.88</v>
+        <v>-0.88</v>
       </c>
       <c r="L68" t="n">
         <v>3.78</v>
@@ -4317,7 +5132,7 @@
         <v>0.96</v>
       </c>
       <c r="N68" t="n">
-        <v>2.51</v>
+        <v>5.49</v>
       </c>
       <c r="O68" t="n">
         <v>1.48</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>12.03</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="H69" t="n">
-        <v>679.85</v>
+        <v>702.6</v>
       </c>
       <c r="I69" t="n">
         <v>697.5630524326342</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.21</v>
+        <v>-5.63</v>
       </c>
       <c r="L69" t="n">
         <v>11.4</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.53</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H70" t="n">
-        <v>787.15</v>
+        <v>723.45</v>
       </c>
       <c r="I70" t="n">
         <v>758.472848841694</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K70" t="n">
-        <v>12.03</v>
+        <v>2.97</v>
       </c>
       <c r="L70" t="n">
         <v>3.86</v>
@@ -4431,7 +5270,7 @@
         <v>1.14</v>
       </c>
       <c r="N70" t="n">
-        <v>2.87</v>
+        <v>8.09</v>
       </c>
       <c r="O70" t="n">
         <v>3.35</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>14.57</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="H71" t="n">
-        <v>747.65</v>
+        <v>765.05</v>
       </c>
       <c r="I71" t="n">
         <v>761.1622119519368</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.35</v>
+        <v>-5.75</v>
       </c>
       <c r="L71" t="n">
         <v>10.13</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="H72" t="n">
-        <v>752.35</v>
+        <v>644.8</v>
       </c>
       <c r="I72" t="n">
         <v>691.9992601238075</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.66</v>
+        <v>-15.72</v>
       </c>
       <c r="L72" t="n">
-        <v>2.67</v>
+        <v>18.23</v>
       </c>
       <c r="M72" t="n">
-        <v>0.65</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>1.66</v>
+        <v>14.3</v>
       </c>
       <c r="O72" t="n">
         <v>2.33</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>19.45</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H73" t="n">
-        <v>643.75</v>
+        <v>659.8</v>
       </c>
       <c r="I73" t="n">
         <v>648.8177099478083</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K73" t="n">
-        <v>0.16</v>
+        <v>-2.33</v>
       </c>
       <c r="L73" t="n">
         <v>10.85</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>10.86</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H74" t="n">
-        <v>611</v>
+        <v>593.75</v>
       </c>
       <c r="I74" t="n">
         <v>609.2813106606779</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.4</v>
+        <v>-10.01</v>
       </c>
       <c r="L74" t="n">
-        <v>8.15</v>
+        <v>10.24</v>
       </c>
       <c r="M74" t="n">
         <v>1.17</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="H75" t="n">
-        <v>597.3</v>
+        <v>625.85</v>
       </c>
       <c r="I75" t="n">
         <v>617.2317894178046</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.6</v>
+        <v>-5.41</v>
       </c>
       <c r="L75" t="n">
-        <v>5.77</v>
+        <v>5.94</v>
       </c>
       <c r="M75" t="n">
         <v>1.45</v>
       </c>
       <c r="N75" t="n">
-        <v>4.19</v>
+        <v>4.78</v>
       </c>
       <c r="O75" t="n">
         <v>-2.82</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>10.61</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="H76" t="n">
-        <v>568.15</v>
+        <v>563</v>
       </c>
       <c r="I76" t="n">
         <v>566.5556102152497</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K76" t="n">
-        <v>-9.220000000000001</v>
+        <v>-10.04</v>
       </c>
       <c r="L76" t="n">
-        <v>9.99</v>
+        <v>10.83</v>
       </c>
       <c r="M76" t="n">
         <v>0.64</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.58</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H77" t="n">
-        <v>524.7</v>
+        <v>541.65</v>
       </c>
       <c r="I77" t="n">
         <v>532.8240522607289</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K77" t="n">
-        <v>6.8</v>
+        <v>3.79</v>
       </c>
       <c r="L77" t="n">
         <v>4.97</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4890,6 +5825,14 @@
       <c r="Q78" t="n">
         <v>10</v>
       </c>
+      <c r="R78" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9848,7 +10791,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.8</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="6">
@@ -9858,7 +10801,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -9868,7 +10811,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
@@ -9878,7 +10821,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9888,7 +10831,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69.8</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="10">
@@ -9898,7 +10841,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="11">
@@ -9908,7 +10851,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -9918,7 +10861,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -9928,7 +10871,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.5</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="14">
@@ -9938,7 +10881,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.19</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="15">
@@ -9948,7 +10891,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.15</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="16">
@@ -9958,7 +10901,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.23</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="17">
@@ -9968,7 +10911,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.43</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="18">
@@ -9978,7 +10921,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.3</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="19">
@@ -9988,7 +10931,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.38</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="20">
@@ -9998,7 +10941,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.78</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="21">
@@ -10008,7 +10951,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.01</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -10018,7 +10961,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -10028,7 +10971,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -10038,7 +10981,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="25">
@@ -10058,7 +11001,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.28</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="27">
@@ -10068,7 +11011,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.74</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="28">
@@ -10078,7 +11021,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
